--- a/awatif/ig/cm-v3-administrative-gender.xlsx
+++ b/awatif/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:38:45+00:00</t>
+    <t>2026-02-24T10:20:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/awatif/ig/cm-v3-administrative-gender.xlsx
+++ b/awatif/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:20:20+00:00</t>
+    <t>2026-02-25T14:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
